--- a/jigyosho/izumo_kaigo_list.xlsx
+++ b/jigyosho/izumo_kaigo_list.xlsx
@@ -36,7 +36,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地域密着型通所介護" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全事業所'!$A$1:$L$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全事業所'!$A$1:$L$437</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>http://www/.izumo-yamayuri</t>
+          <t>http://www.izumo-yamayuri.or.jp/tannki.html</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr"/>
@@ -3120,11 +3120,7 @@
           <t>3290400617</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>http://purelife-shimane.com</t>
-        </is>
-      </c>
+      <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
@@ -3654,11 +3650,7 @@
           <t>3271600524</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>http://purelife-shimane.com/dandan/index</t>
-        </is>
-      </c>
+      <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4307,25 +4299,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4886,7 +4876,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>http://www.asunaro-izumo.or.jp/carehouse/index.html</t>
+          <t>https://www.asunaro-izumo.or.jp/carehouse/</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr"/>
@@ -5539,7 +5529,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>http://www.harasho.co.jp/inquiry/list.html#smile_izumo</t>
+          <t>https://www.harasho.co.jp/company/office/smile-care-office/smile-izumo</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr"/>
@@ -5964,7 +5954,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>http://genkido-info.jimdo.com/</t>
+          <t>https://genkido-info.jimdofree.com/</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr"/>
@@ -8679,7 +8669,7 @@
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>http://www.jaizumo.or.jp/welfare</t>
+          <t>https://jaizumo-fukushikai.jp/</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr"/>
@@ -10570,7 +10560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L438"/>
+  <dimension ref="A1:L437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13182,7 +13172,7 @@
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>http://www.jaizumo.or.jp/welfare</t>
+          <t>https://jaizumo-fukushikai.jp/</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
@@ -13758,7 +13748,7 @@
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>http://www.izumo-tokushukai.jp/homevisit</t>
+          <t>https://www.izumo-tokushukai.jp/homevisit/</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -14022,11 +14012,7 @@
           <t>3260490267</t>
         </is>
       </c>
-      <c r="K66" s="8" t="inlineStr">
-        <is>
-          <t>https://izumo.mypl.net/shop/00000369278/</t>
-        </is>
-      </c>
+      <c r="K66" s="6" t="inlineStr"/>
       <c r="L66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
@@ -15526,7 +15512,7 @@
       </c>
       <c r="K95" s="8" t="inlineStr">
         <is>
-          <t>http://www/kandokai.jp/</t>
+          <t>http://www.kandokai.jp/clinic/</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -17028,11 +17014,7 @@
           <t>3271600532</t>
         </is>
       </c>
-      <c r="K123" s="8" t="inlineStr">
-        <is>
-          <t>http://purelife-shimane.com/dayserv/index</t>
-        </is>
-      </c>
+      <c r="K123" s="6" t="inlineStr"/>
       <c r="L123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
@@ -18152,7 +18134,7 @@
       </c>
       <c r="K144" s="8" t="inlineStr">
         <is>
-          <t>http://www.jaizumo.or.jp/welfare</t>
+          <t>https://jaizumo-fukushikai.jp/</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr"/>
@@ -19268,7 +19250,7 @@
       </c>
       <c r="K165" s="8" t="inlineStr">
         <is>
-          <t>http://www.harasho.co.jp/inquiry/list.html#smile_izumo</t>
+          <t>https://www.harasho.co.jp/company/office/smile-care-office/smile-izumo</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -19738,7 +19720,7 @@
       </c>
       <c r="K174" s="8" t="inlineStr">
         <is>
-          <t>http://genkido-info.jimdo.com/</t>
+          <t>https://genkido-info.jimdofree.com/</t>
         </is>
       </c>
       <c r="L174" s="6" t="inlineStr"/>
@@ -20954,7 +20936,7 @@
       </c>
       <c r="K198" s="8" t="inlineStr">
         <is>
-          <t>http://www/.izumo-yamayuri</t>
+          <t>http://www.izumo-yamayuri.or.jp/tannki.html</t>
         </is>
       </c>
       <c r="L198" s="6" t="inlineStr"/>
@@ -21966,11 +21948,7 @@
           <t>3290400617</t>
         </is>
       </c>
-      <c r="K218" s="8" t="inlineStr">
-        <is>
-          <t>http://purelife-shimane.com</t>
-        </is>
-      </c>
+      <c r="K218" s="6" t="inlineStr"/>
       <c r="L218" s="6" t="inlineStr"/>
     </row>
     <row r="219">
@@ -22560,11 +22538,7 @@
           <t>3271600524</t>
         </is>
       </c>
-      <c r="K230" s="8" t="inlineStr">
-        <is>
-          <t>http://purelife-shimane.com/dandan/index</t>
-        </is>
-      </c>
+      <c r="K230" s="6" t="inlineStr"/>
       <c r="L230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
@@ -23682,7 +23656,7 @@
       </c>
       <c r="K252" s="8" t="inlineStr">
         <is>
-          <t>http://www.asunaro-izumo.or.jp/carehouse/index.html</t>
+          <t>https://www.asunaro-izumo.or.jp/carehouse/</t>
         </is>
       </c>
       <c r="L252" s="6" t="inlineStr"/>
@@ -24196,7 +24170,7 @@
       </c>
       <c r="K262" s="8" t="inlineStr">
         <is>
-          <t>http://www.harasho.co.jp/inquiry/list.html#smile_izumo</t>
+          <t>https://www.harasho.co.jp/company/office/smile-care-office/smile-izumo</t>
         </is>
       </c>
       <c r="L262" s="6" t="inlineStr"/>
@@ -24666,7 +24640,7 @@
       </c>
       <c r="K271" s="8" t="inlineStr">
         <is>
-          <t>http://genkido-info.jimdo.com/</t>
+          <t>https://genkido-info.jimdofree.com/</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -27558,7 +27532,7 @@
       </c>
       <c r="K327" s="8" t="inlineStr">
         <is>
-          <t>http://www.jaizumo.or.jp/welfare</t>
+          <t>https://jaizumo-fukushikai.jp/</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -29566,7 +29540,7 @@
       </c>
       <c r="K366" s="8" t="inlineStr">
         <is>
-          <t>http://www.w-himawari.jp/nursing</t>
+          <t>https://www.w-himawari.jp/kaigo/</t>
         </is>
       </c>
       <c r="L366" s="6" t="inlineStr"/>
@@ -29616,7 +29590,7 @@
       </c>
       <c r="K367" s="8" t="inlineStr">
         <is>
-          <t>http://www.w-himawari.jp/nursing</t>
+          <t>https://www.w-himawari.jp/kaigo/</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -29834,7 +29808,7 @@
       </c>
       <c r="K371" s="8" t="inlineStr">
         <is>
-          <t>http://www.ssw.or.jp/facilities/seniors/tenjin/1476</t>
+          <t>https://www.ssw.or.jp/</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -30100,11 +30074,7 @@
           <t>3290400120</t>
         </is>
       </c>
-      <c r="K376" s="8" t="inlineStr">
-        <is>
-          <t>http://www.asunarohoikuen.ed.jp/top/index.html</t>
-        </is>
-      </c>
+      <c r="K376" s="6" t="inlineStr"/>
       <c r="L376" s="6" t="inlineStr"/>
     </row>
     <row r="377">
@@ -30352,11 +30322,7 @@
           <t>3290400815</t>
         </is>
       </c>
-      <c r="K381" s="8" t="inlineStr">
-        <is>
-          <t>http://yama-boushi.com/</t>
-        </is>
-      </c>
+      <c r="K381" s="6" t="inlineStr"/>
       <c r="L381" s="6" t="inlineStr"/>
     </row>
     <row r="382">
@@ -31083,30 +31049,32 @@
       </c>
       <c r="B396" s="7" t="inlineStr">
         <is>
-          <t>あんのん大社</t>
+          <t>あんのんの里川跡</t>
         </is>
       </c>
       <c r="C396" s="6" t="inlineStr">
         <is>
-          <t>大社</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D396" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市大社町杵築西1735</t>
+          <t>荻杼町666-1</t>
         </is>
       </c>
       <c r="E396" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4780</t>
+          <t>0853-31-4600</t>
         </is>
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4781</t>
-        </is>
-      </c>
-      <c r="G396" s="6" t="inlineStr"/>
+          <t>0853-31-4601</t>
+        </is>
+      </c>
+      <c r="G396" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="H396" s="7" t="inlineStr">
         <is>
           <t>平日,祝日</t>
@@ -31119,7 +31087,7 @@
       </c>
       <c r="J396" s="6" t="inlineStr">
         <is>
-          <t>3290400799</t>
+          <t>3270402138</t>
         </is>
       </c>
       <c r="K396" s="6" t="inlineStr"/>
@@ -31133,7 +31101,7 @@
       </c>
       <c r="B397" s="7" t="inlineStr">
         <is>
-          <t>あんのんの里川跡</t>
+          <t>出雲市里家センター</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
@@ -31143,21 +31111,21 @@
       </c>
       <c r="D397" s="7" t="inlineStr">
         <is>
-          <t>荻杼町666-1</t>
+          <t>出雲市乙立町3162番地</t>
         </is>
       </c>
       <c r="E397" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4600</t>
+          <t>0853-45-0378</t>
         </is>
       </c>
       <c r="F397" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4601</t>
+          <t>0853-45-0370</t>
         </is>
       </c>
       <c r="G397" s="6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H397" s="7" t="inlineStr">
         <is>
@@ -31166,12 +31134,12 @@
       </c>
       <c r="I397" s="7" t="inlineStr">
         <is>
-          <t>株式会社ハート</t>
+          <t>株式会社蔵西</t>
         </is>
       </c>
       <c r="J397" s="6" t="inlineStr">
         <is>
-          <t>3270402138</t>
+          <t>3270401551</t>
         </is>
       </c>
       <c r="K397" s="6" t="inlineStr"/>
@@ -31185,7 +31153,7 @@
       </c>
       <c r="B398" s="7" t="inlineStr">
         <is>
-          <t>出雲市里家センター</t>
+          <t>ウェルファ出雲デイサービスセンターかえで</t>
         </is>
       </c>
       <c r="C398" s="6" t="inlineStr">
@@ -31195,35 +31163,33 @@
       </c>
       <c r="D398" s="7" t="inlineStr">
         <is>
-          <t>出雲市乙立町3162番地</t>
+          <t>島根県出雲市塩冶神前１－６－２７CASA神前１階CASA神前１階</t>
         </is>
       </c>
       <c r="E398" s="6" t="inlineStr">
         <is>
-          <t>0853-45-0378</t>
+          <t>０８５３－２５－７１１０</t>
         </is>
       </c>
       <c r="F398" s="6" t="inlineStr">
         <is>
-          <t>0853-45-0370</t>
-        </is>
-      </c>
-      <c r="G398" s="6" t="n">
-        <v>12</v>
-      </c>
+          <t>０８５３－２５－７００８</t>
+        </is>
+      </c>
+      <c r="G398" s="6" t="inlineStr"/>
       <c r="H398" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="I398" s="7" t="inlineStr">
         <is>
-          <t>株式会社蔵西</t>
+          <t>ボンウエルファ株式会社</t>
         </is>
       </c>
       <c r="J398" s="6" t="inlineStr">
         <is>
-          <t>3270401551</t>
+          <t>3270402666</t>
         </is>
       </c>
       <c r="K398" s="6" t="inlineStr"/>
@@ -31237,7 +31203,7 @@
       </c>
       <c r="B399" s="7" t="inlineStr">
         <is>
-          <t>ウェルファ出雲デイサービスセンターかえで</t>
+          <t>えきまえデイサービス　夢のむら</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
@@ -31247,36 +31213,40 @@
       </c>
       <c r="D399" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市塩冶神前１－６－２７CASA神前１階CASA神前１階</t>
+          <t>出雲市塩冶町　980-3</t>
         </is>
       </c>
       <c r="E399" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２５－７１１０</t>
+          <t>0853-21-0986</t>
         </is>
       </c>
       <c r="F399" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２５－７００８</t>
+          <t>0853-23-0197</t>
         </is>
       </c>
       <c r="G399" s="6" t="inlineStr"/>
       <c r="H399" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="I399" s="7" t="inlineStr">
         <is>
-          <t>ボンウエルファ株式会社</t>
+          <t>有限会社ケアサービス出雲</t>
         </is>
       </c>
       <c r="J399" s="6" t="inlineStr">
         <is>
-          <t>3270402666</t>
-        </is>
-      </c>
-      <c r="K399" s="6" t="inlineStr"/>
+          <t>3270401171</t>
+        </is>
+      </c>
+      <c r="K399" s="8" t="inlineStr">
+        <is>
+          <t>https://care-service-izumo.biz/</t>
+        </is>
+      </c>
       <c r="L399" s="6" t="inlineStr"/>
     </row>
     <row r="400">
@@ -31287,48 +31257,50 @@
       </c>
       <c r="B400" s="7" t="inlineStr">
         <is>
-          <t>えきまえデイサービス　夢のむら</t>
+          <t>NPO法人たすけあい平田デイサービスセンターさわやか</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="D400" s="7" t="inlineStr">
         <is>
-          <t>出雲市塩冶町　980-3</t>
+          <t>島根県出雲市西代町1032-4</t>
         </is>
       </c>
       <c r="E400" s="6" t="inlineStr">
         <is>
-          <t>0853-21-0986</t>
+          <t>0853-31-6500</t>
         </is>
       </c>
       <c r="F400" s="6" t="inlineStr">
         <is>
-          <t>0853-23-0197</t>
-        </is>
-      </c>
-      <c r="G400" s="6" t="inlineStr"/>
+          <t>0853-31-6501</t>
+        </is>
+      </c>
+      <c r="G400" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="H400" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I400" s="7" t="inlineStr">
         <is>
-          <t>有限会社ケアサービス出雲</t>
+          <t>特定非営利活動法人たすけあい平田デイサービスセンターさわやか</t>
         </is>
       </c>
       <c r="J400" s="6" t="inlineStr">
         <is>
-          <t>3270401171</t>
+          <t>3270402781</t>
         </is>
       </c>
       <c r="K400" s="8" t="inlineStr">
         <is>
-          <t>https://care-service-izumo.biz/</t>
+          <t>http://www.npo.lsnet.ne.jp/tasukeaihirata/</t>
         </is>
       </c>
       <c r="L400" s="6" t="inlineStr"/>
@@ -31341,50 +31313,48 @@
       </c>
       <c r="B401" s="7" t="inlineStr">
         <is>
-          <t>NPO法人たすけあい平田デイサービスセンターさわやか</t>
+          <t>介護予防センター　早稲田イーライフ出雲</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D401" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市西代町1032-4</t>
+          <t>大津新崎町1丁目29番地1</t>
         </is>
       </c>
       <c r="E401" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6500</t>
+          <t>0853－25－8412</t>
         </is>
       </c>
       <c r="F401" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6501</t>
-        </is>
-      </c>
-      <c r="G401" s="6" t="n">
-        <v>5</v>
-      </c>
+          <t>0853－25－8413</t>
+        </is>
+      </c>
+      <c r="G401" s="6" t="inlineStr"/>
       <c r="H401" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="I401" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人たすけあい平田デイサービスセンターさわやか</t>
+          <t>株式会社　中林建築設計事務所</t>
         </is>
       </c>
       <c r="J401" s="6" t="inlineStr">
         <is>
-          <t>3270402781</t>
+          <t>3270402310</t>
         </is>
       </c>
       <c r="K401" s="8" t="inlineStr">
         <is>
-          <t>http://www.npo.lsnet.ne.jp/tasukeaihirata/</t>
+          <t>http://www.h-sweet-home.com</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -31397,30 +31367,32 @@
       </c>
       <c r="B402" s="7" t="inlineStr">
         <is>
-          <t>介護予防センター　早稲田イーライフ出雲</t>
+          <t>介護予防センター　早稲田イーライフきらり</t>
         </is>
       </c>
       <c r="C402" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>湖陵</t>
         </is>
       </c>
       <c r="D402" s="7" t="inlineStr">
         <is>
-          <t>大津新崎町1丁目29番地1</t>
+          <t>島根県出雲市湖陵町二部1192番地1</t>
         </is>
       </c>
       <c r="E402" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8412</t>
+          <t>0853-43-8080</t>
         </is>
       </c>
       <c r="F402" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8413</t>
-        </is>
-      </c>
-      <c r="G402" s="6" t="inlineStr"/>
+          <t>0853-43-7006</t>
+        </is>
+      </c>
+      <c r="G402" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="H402" s="7" t="inlineStr">
         <is>
           <t>平日,祝日</t>
@@ -31428,17 +31400,17 @@
       </c>
       <c r="I402" s="7" t="inlineStr">
         <is>
-          <t>株式会社　中林建築設計事務所</t>
+          <t>株式会社中林建築設計事務所</t>
         </is>
       </c>
       <c r="J402" s="6" t="inlineStr">
         <is>
-          <t>3270402310</t>
+          <t>3270401916</t>
         </is>
       </c>
       <c r="K402" s="8" t="inlineStr">
         <is>
-          <t>http://www.h-sweet-home.com</t>
+          <t>http://www.h-sweet-home.com/</t>
         </is>
       </c>
       <c r="L402" s="6" t="inlineStr"/>
@@ -31451,50 +31423,48 @@
       </c>
       <c r="B403" s="7" t="inlineStr">
         <is>
-          <t>介護予防センター　早稲田イーライフきらり</t>
+          <t>ケアサポート　相生</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
         <is>
-          <t>湖陵</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D403" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市湖陵町二部1192番地1</t>
+          <t>出雲市今市町７４１－５</t>
         </is>
       </c>
       <c r="E403" s="6" t="inlineStr">
         <is>
-          <t>0853-43-8080</t>
+          <t>0853-24-7733</t>
         </is>
       </c>
       <c r="F403" s="6" t="inlineStr">
         <is>
-          <t>0853-43-7006</t>
-        </is>
-      </c>
-      <c r="G403" s="6" t="n">
-        <v>100</v>
-      </c>
+          <t>0853-24-7738</t>
+        </is>
+      </c>
+      <c r="G403" s="6" t="inlineStr"/>
       <c r="H403" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I403" s="7" t="inlineStr">
         <is>
-          <t>株式会社中林建築設計事務所</t>
+          <t>社会福祉法人壽光会</t>
         </is>
       </c>
       <c r="J403" s="6" t="inlineStr">
         <is>
-          <t>3270401916</t>
+          <t>3270401114</t>
         </is>
       </c>
       <c r="K403" s="8" t="inlineStr">
         <is>
-          <t>http://www.h-sweet-home.com/</t>
+          <t>https://jukokai.jp/</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -31507,50 +31477,46 @@
       </c>
       <c r="B404" s="7" t="inlineStr">
         <is>
-          <t>ケアサポート　相生</t>
+          <t>ココ・リハ平田</t>
         </is>
       </c>
       <c r="C404" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="D404" s="7" t="inlineStr">
         <is>
-          <t>出雲市今市町７４１－５</t>
+          <t>島根県出雲市西平田町104番地3</t>
         </is>
       </c>
       <c r="E404" s="6" t="inlineStr">
         <is>
-          <t>0853-24-7733</t>
+          <t>0853－25－8400</t>
         </is>
       </c>
       <c r="F404" s="6" t="inlineStr">
         <is>
-          <t>0853-24-7738</t>
+          <t>0853－25－8401</t>
         </is>
       </c>
       <c r="G404" s="6" t="inlineStr"/>
       <c r="H404" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="I404" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人壽光会</t>
+          <t>株式会社　建装</t>
         </is>
       </c>
       <c r="J404" s="6" t="inlineStr">
         <is>
-          <t>3270401114</t>
-        </is>
-      </c>
-      <c r="K404" s="8" t="inlineStr">
-        <is>
-          <t>https://jukokai.jp/</t>
-        </is>
-      </c>
+          <t>3270402336</t>
+        </is>
+      </c>
+      <c r="K404" s="6" t="inlineStr"/>
       <c r="L404" s="6" t="inlineStr"/>
     </row>
     <row r="405">
@@ -31561,46 +31527,52 @@
       </c>
       <c r="B405" s="7" t="inlineStr">
         <is>
-          <t>ココ・リハ平田</t>
+          <t>茶話本舗デイサービス出雲</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D405" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市西平田町104番地3</t>
+          <t>島根県出雲市大津新崎町5-38-1</t>
         </is>
       </c>
       <c r="E405" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8400</t>
+          <t>0853-25-8535</t>
         </is>
       </c>
       <c r="F405" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8401</t>
-        </is>
-      </c>
-      <c r="G405" s="6" t="inlineStr"/>
+          <t>0853-25-8536</t>
+        </is>
+      </c>
+      <c r="G405" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H405" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,日曜日,祝日</t>
         </is>
       </c>
       <c r="I405" s="7" t="inlineStr">
         <is>
-          <t>株式会社　建装</t>
+          <t>株式会社ドリームシアター</t>
         </is>
       </c>
       <c r="J405" s="6" t="inlineStr">
         <is>
-          <t>3270402336</t>
-        </is>
-      </c>
-      <c r="K405" s="6" t="inlineStr"/>
+          <t>3270402534</t>
+        </is>
+      </c>
+      <c r="K405" s="8" t="inlineStr">
+        <is>
+          <t>https://sawaizumo.wixsite.com/home</t>
+        </is>
+      </c>
       <c r="L405" s="6" t="inlineStr"/>
     </row>
     <row r="406">
@@ -31611,7 +31583,7 @@
       </c>
       <c r="B406" s="7" t="inlineStr">
         <is>
-          <t>茶話本舗デイサービス出雲</t>
+          <t>社会福祉法人静和会プライム清流園デイサービスセンター</t>
         </is>
       </c>
       <c r="C406" s="6" t="inlineStr">
@@ -31621,22 +31593,20 @@
       </c>
       <c r="D406" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市大津新崎町5-38-1</t>
+          <t>島根県出雲市大津町3529</t>
         </is>
       </c>
       <c r="E406" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8535</t>
+          <t>0583-25-8356</t>
         </is>
       </c>
       <c r="F406" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8536</t>
-        </is>
-      </c>
-      <c r="G406" s="6" t="n">
-        <v>10</v>
-      </c>
+          <t>0853-25-8376</t>
+        </is>
+      </c>
+      <c r="G406" s="6" t="inlineStr"/>
       <c r="H406" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,日曜日,祝日</t>
@@ -31644,17 +31614,17 @@
       </c>
       <c r="I406" s="7" t="inlineStr">
         <is>
-          <t>株式会社ドリームシアター</t>
+          <t>社会福祉法人静和会</t>
         </is>
       </c>
       <c r="J406" s="6" t="inlineStr">
         <is>
-          <t>3270402534</t>
+          <t>3290400773</t>
         </is>
       </c>
       <c r="K406" s="8" t="inlineStr">
         <is>
-          <t>https://sawaizumo.wixsite.com/home</t>
+          <t>https://www.seiryuuen.com/</t>
         </is>
       </c>
       <c r="L406" s="6" t="inlineStr"/>
@@ -31667,48 +31637,48 @@
       </c>
       <c r="B407" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人静和会プライム清流園デイサービスセンター</t>
+          <t>社会福祉法人やまゆり　通所やまゆり</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>佐田</t>
         </is>
       </c>
       <c r="D407" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市大津町3529</t>
+          <t>島根県出雲市佐田町一窪田1961番地５</t>
         </is>
       </c>
       <c r="E407" s="6" t="inlineStr">
         <is>
-          <t>0583-25-8356</t>
+          <t>0853-85-8100</t>
         </is>
       </c>
       <c r="F407" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8376</t>
+          <t>0853-85-2929</t>
         </is>
       </c>
       <c r="G407" s="6" t="inlineStr"/>
       <c r="H407" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,日曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="I407" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人静和会</t>
+          <t>社会福祉法人やまゆり</t>
         </is>
       </c>
       <c r="J407" s="6" t="inlineStr">
         <is>
-          <t>3290400773</t>
+          <t>3270401361</t>
         </is>
       </c>
       <c r="K407" s="8" t="inlineStr">
         <is>
-          <t>http://www.seiryuuen.com/page533016.html</t>
+          <t>http://www.izumo-yamayuri.or.jp</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -31721,48 +31691,48 @@
       </c>
       <c r="B408" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり　通所やまゆり</t>
+          <t>出東デイサービスセンター</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
         <is>
-          <t>佐田</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="D408" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市佐田町一窪田1961番地５</t>
+          <t>島根県出雲市斐川町三分市1077</t>
         </is>
       </c>
       <c r="E408" s="6" t="inlineStr">
         <is>
-          <t>0853-85-8100</t>
+          <t>0853-63-3777</t>
         </is>
       </c>
       <c r="F408" s="6" t="inlineStr">
         <is>
-          <t>0853-85-2929</t>
+          <t>0853-63-7007</t>
         </is>
       </c>
       <c r="G408" s="6" t="inlineStr"/>
       <c r="H408" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I408" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり</t>
+          <t>社会福祉法人出東福祉会</t>
         </is>
       </c>
       <c r="J408" s="6" t="inlineStr">
         <is>
-          <t>3270401361</t>
+          <t>3271600144</t>
         </is>
       </c>
       <c r="K408" s="8" t="inlineStr">
         <is>
-          <t>http://www.izumo-yamayuri.or.jp</t>
+          <t>https://syuttou-fukushikai.net/day/</t>
         </is>
       </c>
       <c r="L408" s="6" t="inlineStr"/>
@@ -31775,27 +31745,27 @@
       </c>
       <c r="B409" s="7" t="inlineStr">
         <is>
-          <t>出東デイサービスセンター</t>
+          <t>笑庵ことぶき通所介護事業所</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D409" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町三分市1077</t>
+          <t>古志町344</t>
         </is>
       </c>
       <c r="E409" s="6" t="inlineStr">
         <is>
-          <t>0853-63-3777</t>
+          <t>0853-25-7701</t>
         </is>
       </c>
       <c r="F409" s="6" t="inlineStr">
         <is>
-          <t>0853-63-7007</t>
+          <t>0853-25-7702</t>
         </is>
       </c>
       <c r="G409" s="6" t="inlineStr"/>
@@ -31806,17 +31776,17 @@
       </c>
       <c r="I409" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人出東福祉会</t>
+          <t>社会福祉法人ことぶき福祉会</t>
         </is>
       </c>
       <c r="J409" s="6" t="inlineStr">
         <is>
-          <t>3271600144</t>
+          <t>3270401882</t>
         </is>
       </c>
       <c r="K409" s="8" t="inlineStr">
         <is>
-          <t>https://syuttou-fukushikai.net/day/</t>
+          <t>https://kotobuki1071.jimdofree.com/</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -31829,48 +31799,48 @@
       </c>
       <c r="B410" s="7" t="inlineStr">
         <is>
-          <t>笑庵ことぶき通所介護事業所</t>
+          <t>通所　かがやきの家</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>佐田</t>
         </is>
       </c>
       <c r="D410" s="7" t="inlineStr">
         <is>
-          <t>古志町344</t>
+          <t>島根県出雲市佐田町須佐736番地2</t>
         </is>
       </c>
       <c r="E410" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7701</t>
+          <t>0853-84-9300</t>
         </is>
       </c>
       <c r="F410" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7702</t>
+          <t>0853-84-9300</t>
         </is>
       </c>
       <c r="G410" s="6" t="inlineStr"/>
       <c r="H410" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="I410" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人ことぶき福祉会</t>
+          <t>社会福祉法人やまゆり</t>
         </is>
       </c>
       <c r="J410" s="6" t="inlineStr">
         <is>
-          <t>3270401882</t>
+          <t>3270401403</t>
         </is>
       </c>
       <c r="K410" s="8" t="inlineStr">
         <is>
-          <t>https://kotobuki1071.jimdofree.com/</t>
+          <t>http://www.izumo-yamayuri.or.jp</t>
         </is>
       </c>
       <c r="L410" s="6" t="inlineStr"/>
@@ -31883,50 +31853,48 @@
       </c>
       <c r="B411" s="7" t="inlineStr">
         <is>
-          <t>通所　かがやきの家</t>
+          <t>通所介護長浜味覚亭</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
         <is>
-          <t>佐田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D411" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市佐田町須佐736番地2</t>
+          <t>出雲市西園町500番地1</t>
         </is>
       </c>
       <c r="E411" s="6" t="inlineStr">
         <is>
-          <t>0853-84-9300</t>
+          <t>0853-28-2828</t>
         </is>
       </c>
       <c r="F411" s="6" t="inlineStr">
         <is>
-          <t>0853-84-9300</t>
-        </is>
-      </c>
-      <c r="G411" s="6" t="inlineStr"/>
+          <t>0853-28-2028</t>
+        </is>
+      </c>
+      <c r="G411" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="H411" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I411" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり</t>
+          <t>株式会社蔵西</t>
         </is>
       </c>
       <c r="J411" s="6" t="inlineStr">
         <is>
-          <t>3270401403</t>
-        </is>
-      </c>
-      <c r="K411" s="8" t="inlineStr">
-        <is>
-          <t>http://www.izumo-yamayuri.or.jp</t>
-        </is>
-      </c>
+          <t>3270401288</t>
+        </is>
+      </c>
+      <c r="K411" s="6" t="inlineStr"/>
       <c r="L411" s="6" t="inlineStr"/>
     </row>
     <row r="412">
@@ -31937,7 +31905,7 @@
       </c>
       <c r="B412" s="7" t="inlineStr">
         <is>
-          <t>通所介護長浜味覚亭</t>
+          <t>デイサービス　こひまり</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
@@ -31947,22 +31915,20 @@
       </c>
       <c r="D412" s="7" t="inlineStr">
         <is>
-          <t>出雲市西園町500番地1</t>
+          <t>島根県出雲市馬木町224-1</t>
         </is>
       </c>
       <c r="E412" s="6" t="inlineStr">
         <is>
-          <t>0853-28-2828</t>
+          <t>０８５３－４８－９０５７</t>
         </is>
       </c>
       <c r="F412" s="6" t="inlineStr">
         <is>
-          <t>0853-28-2028</t>
-        </is>
-      </c>
-      <c r="G412" s="6" t="n">
-        <v>18</v>
-      </c>
+          <t>０８５３－４８－００４７</t>
+        </is>
+      </c>
+      <c r="G412" s="6" t="inlineStr"/>
       <c r="H412" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -31970,12 +31936,12 @@
       </c>
       <c r="I412" s="7" t="inlineStr">
         <is>
-          <t>株式会社蔵西</t>
+          <t>株式会社ひまり</t>
         </is>
       </c>
       <c r="J412" s="6" t="inlineStr">
         <is>
-          <t>3270401288</t>
+          <t>3290400567</t>
         </is>
       </c>
       <c r="K412" s="6" t="inlineStr"/>
@@ -31989,7 +31955,7 @@
       </c>
       <c r="B413" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　こひまり</t>
+          <t>デイサービス　グッドライフ</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
@@ -31999,20 +31965,22 @@
       </c>
       <c r="D413" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市馬木町224-1</t>
+          <t>島根県出雲市塩冶善行町14-3</t>
         </is>
       </c>
       <c r="E413" s="6" t="inlineStr">
         <is>
-          <t>０８５３－４８－９０５７</t>
+          <t>0853-27-9991</t>
         </is>
       </c>
       <c r="F413" s="6" t="inlineStr">
         <is>
-          <t>０８５３－４８－００４７</t>
-        </is>
-      </c>
-      <c r="G413" s="6" t="inlineStr"/>
+          <t>0853-27-9992</t>
+        </is>
+      </c>
+      <c r="G413" s="6" t="n">
+        <v>15</v>
+      </c>
       <c r="H413" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -32020,15 +31988,19 @@
       </c>
       <c r="I413" s="7" t="inlineStr">
         <is>
-          <t>株式会社ひまり</t>
+          <t>株式会社　コスモス</t>
         </is>
       </c>
       <c r="J413" s="6" t="inlineStr">
         <is>
-          <t>3290400567</t>
-        </is>
-      </c>
-      <c r="K413" s="6" t="inlineStr"/>
+          <t>3270402120</t>
+        </is>
+      </c>
+      <c r="K413" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cosmos-izumo.jp</t>
+        </is>
+      </c>
       <c r="L413" s="6" t="inlineStr"/>
     </row>
     <row r="414">
@@ -32039,7 +32011,7 @@
       </c>
       <c r="B414" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　グッドライフ</t>
+          <t>デイサービス　さくら</t>
         </is>
       </c>
       <c r="C414" s="6" t="inlineStr">
@@ -32049,22 +32021,20 @@
       </c>
       <c r="D414" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市塩冶善行町14-3</t>
+          <t>矢尾町273番地プライム有限会社プライム有限会社</t>
         </is>
       </c>
       <c r="E414" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9991</t>
+          <t>0853-25-0027</t>
         </is>
       </c>
       <c r="F414" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9992</t>
-        </is>
-      </c>
-      <c r="G414" s="6" t="n">
-        <v>15</v>
-      </c>
+          <t>0853-25-0020</t>
+        </is>
+      </c>
+      <c r="G414" s="6" t="inlineStr"/>
       <c r="H414" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -32072,19 +32042,15 @@
       </c>
       <c r="I414" s="7" t="inlineStr">
         <is>
-          <t>株式会社　コスモス</t>
+          <t>プライム有限会社</t>
         </is>
       </c>
       <c r="J414" s="6" t="inlineStr">
         <is>
-          <t>3270402120</t>
-        </is>
-      </c>
-      <c r="K414" s="8" t="inlineStr">
-        <is>
-          <t>https://www.cosmos-izumo.jp</t>
-        </is>
-      </c>
+          <t>3270402641</t>
+        </is>
+      </c>
+      <c r="K414" s="6" t="inlineStr"/>
       <c r="L414" s="6" t="inlineStr"/>
     </row>
     <row r="415">
@@ -32095,7 +32061,7 @@
       </c>
       <c r="B415" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　さくら</t>
+          <t>デイサービス　なすの花</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
@@ -32105,17 +32071,17 @@
       </c>
       <c r="D415" s="7" t="inlineStr">
         <is>
-          <t>矢尾町273番地プライム有限会社プライム有限会社</t>
+          <t>島根県出雲市白枝町７８１－８</t>
         </is>
       </c>
       <c r="E415" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0027</t>
+          <t>０８５３－２０－１２８８</t>
         </is>
       </c>
       <c r="F415" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0020</t>
+          <t>０８５３－２０－１２８７</t>
         </is>
       </c>
       <c r="G415" s="6" t="inlineStr"/>
@@ -32126,12 +32092,12 @@
       </c>
       <c r="I415" s="7" t="inlineStr">
         <is>
-          <t>プライム有限会社</t>
+          <t>株式会社スマイル・ガーデン</t>
         </is>
       </c>
       <c r="J415" s="6" t="inlineStr">
         <is>
-          <t>3270402641</t>
+          <t>3270401635</t>
         </is>
       </c>
       <c r="K415" s="6" t="inlineStr"/>
@@ -32145,7 +32111,7 @@
       </c>
       <c r="B416" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　なすの花</t>
+          <t>デイサービス　春の野</t>
         </is>
       </c>
       <c r="C416" s="6" t="inlineStr">
@@ -32155,36 +32121,42 @@
       </c>
       <c r="D416" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市白枝町７８１－８</t>
+          <t>島根県出雲市小山町３３４番地板倉ビル１０３号室板倉ビル１０３号室</t>
         </is>
       </c>
       <c r="E416" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２０－１２８８</t>
+          <t>0853-25-8550</t>
         </is>
       </c>
       <c r="F416" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２０－１２８７</t>
-        </is>
-      </c>
-      <c r="G416" s="6" t="inlineStr"/>
+          <t>0853-25-8550</t>
+        </is>
+      </c>
+      <c r="G416" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="H416" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="I416" s="7" t="inlineStr">
         <is>
-          <t>株式会社スマイル・ガーデン</t>
+          <t>株式会社ＨＯＬＹ</t>
         </is>
       </c>
       <c r="J416" s="6" t="inlineStr">
         <is>
-          <t>3270401635</t>
-        </is>
-      </c>
-      <c r="K416" s="6" t="inlineStr"/>
+          <t>3290400781</t>
+        </is>
+      </c>
+      <c r="K416" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/デイサービス春の野/100094930075195/</t>
+        </is>
+      </c>
       <c r="L416" s="6" t="inlineStr"/>
     </row>
     <row r="417">
@@ -32195,7 +32167,7 @@
       </c>
       <c r="B417" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　春の野</t>
+          <t>ﾃﾞｲｻｰﾋﾞｽ　ひまり</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
@@ -32205,42 +32177,36 @@
       </c>
       <c r="D417" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市小山町３３４番地板倉ビル１０３号室板倉ビル１０３号室</t>
+          <t>出雲市馬木町７５８番地２</t>
         </is>
       </c>
       <c r="E417" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8550</t>
+          <t>0853-48-9135</t>
         </is>
       </c>
       <c r="F417" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8550</t>
-        </is>
-      </c>
-      <c r="G417" s="6" t="n">
-        <v>20</v>
-      </c>
+          <t>0853-48-2670</t>
+        </is>
+      </c>
+      <c r="G417" s="6" t="inlineStr"/>
       <c r="H417" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I417" s="7" t="inlineStr">
         <is>
-          <t>株式会社ＨＯＬＹ</t>
+          <t>株式会社ひまり</t>
         </is>
       </c>
       <c r="J417" s="6" t="inlineStr">
         <is>
-          <t>3290400781</t>
-        </is>
-      </c>
-      <c r="K417" s="8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/people/デイサービス春の野/100094930075195/</t>
-        </is>
-      </c>
+          <t>3270402047</t>
+        </is>
+      </c>
+      <c r="K417" s="6" t="inlineStr"/>
       <c r="L417" s="6" t="inlineStr"/>
     </row>
     <row r="418">
@@ -32251,7 +32217,7 @@
       </c>
       <c r="B418" s="7" t="inlineStr">
         <is>
-          <t>ﾃﾞｲｻｰﾋﾞｽ　ひまり</t>
+          <t>デイサービス　ゆうらいふ</t>
         </is>
       </c>
       <c r="C418" s="6" t="inlineStr">
@@ -32261,36 +32227,42 @@
       </c>
       <c r="D418" s="7" t="inlineStr">
         <is>
-          <t>出雲市馬木町７５８番地２</t>
+          <t>島根県出雲市荒茅町3501</t>
         </is>
       </c>
       <c r="E418" s="6" t="inlineStr">
         <is>
-          <t>0853-48-9135</t>
+          <t>0853-28-0385</t>
         </is>
       </c>
       <c r="F418" s="6" t="inlineStr">
         <is>
-          <t>0853-48-2670</t>
-        </is>
-      </c>
-      <c r="G418" s="6" t="inlineStr"/>
+          <t>0853-28-0339</t>
+        </is>
+      </c>
+      <c r="G418" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="H418" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="I418" s="7" t="inlineStr">
         <is>
-          <t>株式会社ひまり</t>
+          <t>株式会社ライフサポート</t>
         </is>
       </c>
       <c r="J418" s="6" t="inlineStr">
         <is>
-          <t>3270402047</t>
-        </is>
-      </c>
-      <c r="K418" s="6" t="inlineStr"/>
+          <t>3270401437</t>
+        </is>
+      </c>
+      <c r="K418" s="8" t="inlineStr">
+        <is>
+          <t>http://youlife-n.com</t>
+        </is>
+      </c>
       <c r="L418" s="6" t="inlineStr"/>
     </row>
     <row r="419">
@@ -32301,50 +32273,50 @@
       </c>
       <c r="B419" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　ゆうらいふ</t>
+          <t>デイサービス金太郎の家やまぶき</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="D419" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市荒茅町3501</t>
+          <t>島根県出雲市斐川町学頭1511番地1金太郎の家金太郎の家</t>
         </is>
       </c>
       <c r="E419" s="6" t="inlineStr">
         <is>
-          <t>0853-28-0385</t>
+          <t>0853-72-5110</t>
         </is>
       </c>
       <c r="F419" s="6" t="inlineStr">
         <is>
-          <t>0853-28-0339</t>
+          <t>0853-72-5192</t>
         </is>
       </c>
       <c r="G419" s="6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H419" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I419" s="7" t="inlineStr">
         <is>
-          <t>株式会社ライフサポート</t>
+          <t>社会福祉法人金太郎の家</t>
         </is>
       </c>
       <c r="J419" s="6" t="inlineStr">
         <is>
-          <t>3270401437</t>
+          <t>3270402419</t>
         </is>
       </c>
       <c r="K419" s="8" t="inlineStr">
         <is>
-          <t>http://youlife-n.com</t>
+          <t>https://www.kintarounoie.jp/</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -32357,7 +32329,7 @@
       </c>
       <c r="B420" s="7" t="inlineStr">
         <is>
-          <t>デイサービス金太郎の家やまぶき</t>
+          <t>デイサービス新川</t>
         </is>
       </c>
       <c r="C420" s="6" t="inlineStr">
@@ -32367,17 +32339,17 @@
       </c>
       <c r="D420" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町学頭1511番地1金太郎の家金太郎の家</t>
+          <t>島根県出雲市斐川町大字上庄原字上新川1634番地5</t>
         </is>
       </c>
       <c r="E420" s="6" t="inlineStr">
         <is>
-          <t>0853-72-5110</t>
+          <t>0853-73-7363</t>
         </is>
       </c>
       <c r="F420" s="6" t="inlineStr">
         <is>
-          <t>0853-72-5192</t>
+          <t>0853-73-7363</t>
         </is>
       </c>
       <c r="G420" s="6" t="n">
@@ -32385,22 +32357,22 @@
       </c>
       <c r="H420" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="I420" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人金太郎の家</t>
+          <t>株式会社ハピネライフ一光</t>
         </is>
       </c>
       <c r="J420" s="6" t="inlineStr">
         <is>
-          <t>3270402419</t>
+          <t>3271600664</t>
         </is>
       </c>
       <c r="K420" s="8" t="inlineStr">
         <is>
-          <t>https://www.kintarounoie.jp/</t>
+          <t>http://www.h-ikkou.co.jp</t>
         </is>
       </c>
       <c r="L420" s="6" t="inlineStr"/>
@@ -32413,50 +32385,50 @@
       </c>
       <c r="B421" s="7" t="inlineStr">
         <is>
-          <t>デイサービス新川</t>
+          <t>デイサービス寿生の家</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D421" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町大字上庄原字上新川1634番地5</t>
+          <t>出雲市上塩冶町2854-5</t>
         </is>
       </c>
       <c r="E421" s="6" t="inlineStr">
         <is>
-          <t>0853-73-7363</t>
+          <t>0853-25-0241</t>
         </is>
       </c>
       <c r="F421" s="6" t="inlineStr">
         <is>
-          <t>0853-73-7363</t>
+          <t>0853-25-0285</t>
         </is>
       </c>
       <c r="G421" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H421" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="I421" s="7" t="inlineStr">
         <is>
-          <t>株式会社ハピネライフ一光</t>
+          <t>壽生会</t>
         </is>
       </c>
       <c r="J421" s="6" t="inlineStr">
         <is>
-          <t>3271600664</t>
+          <t>3270401411</t>
         </is>
       </c>
       <c r="K421" s="8" t="inlineStr">
         <is>
-          <t>http://www.h-ikkou.co.jp</t>
+          <t>http://juseikai.jp/</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -32469,7 +32441,7 @@
       </c>
       <c r="B422" s="7" t="inlineStr">
         <is>
-          <t>デイサービス寿生の家</t>
+          <t>デイサービスセンター翔雲</t>
         </is>
       </c>
       <c r="C422" s="6" t="inlineStr">
@@ -32479,42 +32451,36 @@
       </c>
       <c r="D422" s="7" t="inlineStr">
         <is>
-          <t>出雲市上塩冶町2854-5</t>
+          <t>島根県出雲市今市町822-22</t>
         </is>
       </c>
       <c r="E422" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0241</t>
+          <t>0853-21‐5582</t>
         </is>
       </c>
       <c r="F422" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0285</t>
-        </is>
-      </c>
-      <c r="G422" s="6" t="n">
-        <v>15</v>
-      </c>
+          <t>0853-23-5584</t>
+        </is>
+      </c>
+      <c r="G422" s="6" t="inlineStr"/>
       <c r="H422" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="I422" s="7" t="inlineStr">
         <is>
-          <t>壽生会</t>
+          <t>株式会社高砂屋</t>
         </is>
       </c>
       <c r="J422" s="6" t="inlineStr">
         <is>
-          <t>3270401411</t>
-        </is>
-      </c>
-      <c r="K422" s="8" t="inlineStr">
-        <is>
-          <t>http://juseikai.jp/</t>
-        </is>
-      </c>
+          <t>3290400765</t>
+        </is>
+      </c>
+      <c r="K422" s="6" t="inlineStr"/>
       <c r="L422" s="6" t="inlineStr"/>
     </row>
     <row r="423">
@@ -32525,7 +32491,7 @@
       </c>
       <c r="B423" s="7" t="inlineStr">
         <is>
-          <t>デイサービスセンター翔雲</t>
+          <t>デイサービスセンター高砂</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
@@ -32535,12 +32501,12 @@
       </c>
       <c r="D423" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市今市町822-22</t>
+          <t>島根県出雲市今市町822番地22</t>
         </is>
       </c>
       <c r="E423" s="6" t="inlineStr">
         <is>
-          <t>0853-21‐5582</t>
+          <t>0853-21-5582</t>
         </is>
       </c>
       <c r="F423" s="6" t="inlineStr">
@@ -32561,7 +32527,7 @@
       </c>
       <c r="J423" s="6" t="inlineStr">
         <is>
-          <t>3290400765</t>
+          <t>3290400716</t>
         </is>
       </c>
       <c r="K423" s="6" t="inlineStr"/>
@@ -32575,43 +32541,43 @@
       </c>
       <c r="B424" s="7" t="inlineStr">
         <is>
-          <t>デイサービスセンター高砂</t>
+          <t>デイサービス向日葵の家</t>
         </is>
       </c>
       <c r="C424" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="D424" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市今市町822番地22</t>
+          <t>出雲市斐川町荘原3169-28</t>
         </is>
       </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
-          <t>0853-21-5582</t>
+          <t>0853-72-5109</t>
         </is>
       </c>
       <c r="F424" s="6" t="inlineStr">
         <is>
-          <t>0853-23-5584</t>
+          <t>0853-27-9737</t>
         </is>
       </c>
       <c r="G424" s="6" t="inlineStr"/>
       <c r="H424" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I424" s="7" t="inlineStr">
         <is>
-          <t>株式会社高砂屋</t>
+          <t>有限会社　司</t>
         </is>
       </c>
       <c r="J424" s="6" t="inlineStr">
         <is>
-          <t>3290400716</t>
+          <t>3271600565</t>
         </is>
       </c>
       <c r="K424" s="6" t="inlineStr"/>
@@ -32625,7 +32591,7 @@
       </c>
       <c r="B425" s="7" t="inlineStr">
         <is>
-          <t>デイサービス向日葵の家</t>
+          <t>デイサービスMILK新</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
@@ -32635,20 +32601,22 @@
       </c>
       <c r="D425" s="7" t="inlineStr">
         <is>
-          <t>出雲市斐川町荘原3169-28</t>
+          <t>島根県出雲市斐川町上庄原1649番地</t>
         </is>
       </c>
       <c r="E425" s="6" t="inlineStr">
         <is>
-          <t>0853-72-5109</t>
+          <t>0853-31-9722</t>
         </is>
       </c>
       <c r="F425" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9737</t>
-        </is>
-      </c>
-      <c r="G425" s="6" t="inlineStr"/>
+          <t>0853-31-9733</t>
+        </is>
+      </c>
+      <c r="G425" s="6" t="n">
+        <v>25</v>
+      </c>
       <c r="H425" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -32656,12 +32624,12 @@
       </c>
       <c r="I425" s="7" t="inlineStr">
         <is>
-          <t>有限会社　司</t>
+          <t>株式会社　Care　Innovation</t>
         </is>
       </c>
       <c r="J425" s="6" t="inlineStr">
         <is>
-          <t>3271600565</t>
+          <t>3290400526</t>
         </is>
       </c>
       <c r="K425" s="6" t="inlineStr"/>
@@ -32675,31 +32643,31 @@
       </c>
       <c r="B426" s="7" t="inlineStr">
         <is>
-          <t>デイサービスMILK新</t>
+          <t>デイサービスもくれん</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D426" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町上庄原1649番地</t>
+          <t>出雲市松寄下町1286－1</t>
         </is>
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>0853-31-9722</t>
+          <t>0853-25-7230</t>
         </is>
       </c>
       <c r="F426" s="6" t="inlineStr">
         <is>
-          <t>0853-31-9733</t>
+          <t>0853-25-7231</t>
         </is>
       </c>
       <c r="G426" s="6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H426" s="7" t="inlineStr">
         <is>
@@ -32708,16 +32676,24 @@
       </c>
       <c r="I426" s="7" t="inlineStr">
         <is>
-          <t>株式会社　Care　Innovation</t>
+          <t>株式会社もくれん</t>
         </is>
       </c>
       <c r="J426" s="6" t="inlineStr">
         <is>
-          <t>3290400526</t>
-        </is>
-      </c>
-      <c r="K426" s="6" t="inlineStr"/>
-      <c r="L426" s="6" t="inlineStr"/>
+          <t>3270401528</t>
+        </is>
+      </c>
+      <c r="K426" s="8" t="inlineStr">
+        <is>
+          <t>https://www.izumo-mokuren.com/</t>
+        </is>
+      </c>
+      <c r="L426" s="8" t="inlineStr">
+        <is>
+          <t>https://www.izumo-mokuren.com/price/</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
@@ -32727,7 +32703,7 @@
       </c>
       <c r="B427" s="7" t="inlineStr">
         <is>
-          <t>デイサービスもくれん</t>
+          <t>デイサービスもくれん・荒茅</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
@@ -32737,21 +32713,21 @@
       </c>
       <c r="D427" s="7" t="inlineStr">
         <is>
-          <t>出雲市松寄下町1286－1</t>
+          <t>出雲市荒茅町2780番地32</t>
         </is>
       </c>
       <c r="E427" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7230</t>
+          <t>0853-27-9651</t>
         </is>
       </c>
       <c r="F427" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7231</t>
+          <t>0853-27-9652</t>
         </is>
       </c>
       <c r="G427" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H427" s="7" t="inlineStr">
         <is>
@@ -32765,7 +32741,7 @@
       </c>
       <c r="J427" s="6" t="inlineStr">
         <is>
-          <t>3270401528</t>
+          <t>3270401965</t>
         </is>
       </c>
       <c r="K427" s="8" t="inlineStr">
@@ -32787,7 +32763,7 @@
       </c>
       <c r="B428" s="7" t="inlineStr">
         <is>
-          <t>デイサービスもくれん・荒茅</t>
+          <t>デイサービスゆうゆう広場</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
@@ -32797,21 +32773,21 @@
       </c>
       <c r="D428" s="7" t="inlineStr">
         <is>
-          <t>出雲市荒茅町2780番地32</t>
+          <t>知井宮町５－１</t>
         </is>
       </c>
       <c r="E428" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9651</t>
+          <t>0853-23-8762</t>
         </is>
       </c>
       <c r="F428" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9652</t>
+          <t>0853-22-8491</t>
         </is>
       </c>
       <c r="G428" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H428" s="7" t="inlineStr">
         <is>
@@ -32820,24 +32796,20 @@
       </c>
       <c r="I428" s="7" t="inlineStr">
         <is>
-          <t>株式会社もくれん</t>
+          <t>エイコー電子工業株式会社</t>
         </is>
       </c>
       <c r="J428" s="6" t="inlineStr">
         <is>
-          <t>3270401965</t>
+          <t>3270401650</t>
         </is>
       </c>
       <c r="K428" s="8" t="inlineStr">
         <is>
-          <t>https://www.izumo-mokuren.com/</t>
-        </is>
-      </c>
-      <c r="L428" s="8" t="inlineStr">
-        <is>
-          <t>https://www.izumo-mokuren.com/price/</t>
-        </is>
-      </c>
+          <t>https://eikoh-elc.com</t>
+        </is>
+      </c>
+      <c r="L428" s="6" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="6" t="inlineStr">
@@ -32847,7 +32819,7 @@
       </c>
       <c r="B429" s="7" t="inlineStr">
         <is>
-          <t>デイサービスゆうゆう広場</t>
+          <t>ハピネデイサービスセンター出雲</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
@@ -32857,21 +32829,21 @@
       </c>
       <c r="D429" s="7" t="inlineStr">
         <is>
-          <t>知井宮町５－１</t>
+          <t>出雲市渡橋町303番地3</t>
         </is>
       </c>
       <c r="E429" s="6" t="inlineStr">
         <is>
-          <t>0853-23-8762</t>
+          <t>0853-23-8840</t>
         </is>
       </c>
       <c r="F429" s="6" t="inlineStr">
         <is>
-          <t>0853-22-8491</t>
+          <t>0853-23-2269</t>
         </is>
       </c>
       <c r="G429" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H429" s="7" t="inlineStr">
         <is>
@@ -32880,17 +32852,17 @@
       </c>
       <c r="I429" s="7" t="inlineStr">
         <is>
-          <t>エイコー電子工業株式会社</t>
+          <t>株式会社ハピネライフ一光</t>
         </is>
       </c>
       <c r="J429" s="6" t="inlineStr">
         <is>
-          <t>3270401650</t>
+          <t>3270400538</t>
         </is>
       </c>
       <c r="K429" s="8" t="inlineStr">
         <is>
-          <t>https://eikoh-elc.com</t>
+          <t>https://www.hapine.com/</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -32903,7 +32875,7 @@
       </c>
       <c r="B430" s="7" t="inlineStr">
         <is>
-          <t>ハピネデイサービスセンター出雲</t>
+          <t>稗原デイサービスセンター　やまゆり</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
@@ -32913,40 +32885,38 @@
       </c>
       <c r="D430" s="7" t="inlineStr">
         <is>
-          <t>出雲市渡橋町303番地3</t>
+          <t>島根県出雲市稗原町1724番地</t>
         </is>
       </c>
       <c r="E430" s="6" t="inlineStr">
         <is>
-          <t>0853-23-8840</t>
+          <t>0853-77-2497</t>
         </is>
       </c>
       <c r="F430" s="6" t="inlineStr">
         <is>
-          <t>0853-23-2269</t>
-        </is>
-      </c>
-      <c r="G430" s="6" t="n">
-        <v>15</v>
-      </c>
+          <t>0853-77-2497</t>
+        </is>
+      </c>
+      <c r="G430" s="6" t="inlineStr"/>
       <c r="H430" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="I430" s="7" t="inlineStr">
         <is>
-          <t>株式会社ハピネライフ一光</t>
+          <t>社会福祉法人やまゆり</t>
         </is>
       </c>
       <c r="J430" s="6" t="inlineStr">
         <is>
-          <t>3270400538</t>
+          <t>3290400708</t>
         </is>
       </c>
       <c r="K430" s="8" t="inlineStr">
         <is>
-          <t>https://www.hapine.com/</t>
+          <t>http://www.izumo-yamayuri.or.jp</t>
         </is>
       </c>
       <c r="L430" s="6" t="inlineStr"/>
@@ -32959,48 +32929,48 @@
       </c>
       <c r="B431" s="7" t="inlineStr">
         <is>
-          <t>稗原デイサービスセンター　やまゆり</t>
+          <t>ひかわ生協デイサービス　ふらみんご</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="D431" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市稗原町1724番地</t>
+          <t>島根県出雲市斐川町直江４８８３番地１</t>
         </is>
       </c>
       <c r="E431" s="6" t="inlineStr">
         <is>
-          <t>0853-77-2497</t>
+          <t>0853-72-0353</t>
         </is>
       </c>
       <c r="F431" s="6" t="inlineStr">
         <is>
-          <t>0853-77-2497</t>
+          <t>0853-72-0322</t>
         </is>
       </c>
       <c r="G431" s="6" t="inlineStr"/>
       <c r="H431" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I431" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり</t>
+          <t>ひかわ医療生活協同組合</t>
         </is>
       </c>
       <c r="J431" s="6" t="inlineStr">
         <is>
-          <t>3290400708</t>
+          <t>3271600656</t>
         </is>
       </c>
       <c r="K431" s="8" t="inlineStr">
         <is>
-          <t>http://www.izumo-yamayuri.or.jp</t>
+          <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -33013,50 +32983,46 @@
       </c>
       <c r="B432" s="7" t="inlineStr">
         <is>
-          <t>ひかわ生協デイサービス　ふらみんご</t>
+          <t>フロディいずも</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D432" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町直江４８８３番地１</t>
+          <t>塩冶有原町５丁目３６番地</t>
         </is>
       </c>
       <c r="E432" s="6" t="inlineStr">
         <is>
-          <t>0853-72-0353</t>
+          <t>0853-25-7711</t>
         </is>
       </c>
       <c r="F432" s="6" t="inlineStr">
         <is>
-          <t>0853-72-0322</t>
+          <t>0853-25-7791</t>
         </is>
       </c>
       <c r="G432" s="6" t="inlineStr"/>
       <c r="H432" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="I432" s="7" t="inlineStr">
         <is>
-          <t>ひかわ医療生活協同組合</t>
+          <t>フロディ出雲</t>
         </is>
       </c>
       <c r="J432" s="6" t="inlineStr">
         <is>
-          <t>3271600656</t>
-        </is>
-      </c>
-      <c r="K432" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com</t>
-        </is>
-      </c>
+          <t>3290400583</t>
+        </is>
+      </c>
+      <c r="K432" s="6" t="inlineStr"/>
       <c r="L432" s="6" t="inlineStr"/>
     </row>
     <row r="433">
@@ -33067,46 +33033,52 @@
       </c>
       <c r="B433" s="7" t="inlineStr">
         <is>
-          <t>フロディいずも</t>
+          <t>穂なみデイサービスセンターひかわ</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="D433" s="7" t="inlineStr">
         <is>
-          <t>塩冶有原町５丁目３６番地</t>
+          <t>島根県出雲市斐川町上直江２４３－３</t>
         </is>
       </c>
       <c r="E433" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7711</t>
+          <t>0853-25-7946</t>
         </is>
       </c>
       <c r="F433" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7791</t>
-        </is>
-      </c>
-      <c r="G433" s="6" t="inlineStr"/>
+          <t>0853-25-7948</t>
+        </is>
+      </c>
+      <c r="G433" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="H433" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="I433" s="7" t="inlineStr">
         <is>
-          <t>フロディ出雲</t>
+          <t>特定非営利活動法人コミュニティサポートいずも</t>
         </is>
       </c>
       <c r="J433" s="6" t="inlineStr">
         <is>
-          <t>3290400583</t>
-        </is>
-      </c>
-      <c r="K433" s="6" t="inlineStr"/>
+          <t>3290400674</t>
+        </is>
+      </c>
+      <c r="K433" s="8" t="inlineStr">
+        <is>
+          <t>http://cs-izumo.jp/</t>
+        </is>
+      </c>
       <c r="L433" s="6" t="inlineStr"/>
     </row>
     <row r="434">
@@ -33117,32 +33089,30 @@
       </c>
       <c r="B434" s="7" t="inlineStr">
         <is>
-          <t>穂なみデイサービスセンターひかわ</t>
+          <t>穂なみデイサービスセンターひらた</t>
         </is>
       </c>
       <c r="C434" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="D434" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町上直江２４３－３</t>
+          <t>島根県出雲市平田町1953－3</t>
         </is>
       </c>
       <c r="E434" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7946</t>
+          <t>0853－62－9365</t>
         </is>
       </c>
       <c r="F434" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7948</t>
-        </is>
-      </c>
-      <c r="G434" s="6" t="n">
-        <v>18</v>
-      </c>
+          <t>0853－62－9366</t>
+        </is>
+      </c>
+      <c r="G434" s="6" t="inlineStr"/>
       <c r="H434" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -33155,14 +33125,10 @@
       </c>
       <c r="J434" s="6" t="inlineStr">
         <is>
-          <t>3290400674</t>
-        </is>
-      </c>
-      <c r="K434" s="8" t="inlineStr">
-        <is>
-          <t>http://cs-izumo.jp/</t>
-        </is>
-      </c>
+          <t>3290400757</t>
+        </is>
+      </c>
+      <c r="K434" s="6" t="inlineStr"/>
       <c r="L434" s="6" t="inlineStr"/>
     </row>
     <row r="435">
@@ -33173,27 +33139,27 @@
       </c>
       <c r="B435" s="7" t="inlineStr">
         <is>
-          <t>穂なみデイサービスセンターひらた</t>
+          <t>穂なみデイサービスセンターみなみ</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="D435" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市平田町1953－3</t>
+          <t>里方町116番地</t>
         </is>
       </c>
       <c r="E435" s="6" t="inlineStr">
         <is>
-          <t>0853－62－9365</t>
+          <t>0853-20-1218</t>
         </is>
       </c>
       <c r="F435" s="6" t="inlineStr">
         <is>
-          <t>0853－62－9366</t>
+          <t>0853-20-1219</t>
         </is>
       </c>
       <c r="G435" s="6" t="inlineStr"/>
@@ -33209,10 +33175,14 @@
       </c>
       <c r="J435" s="6" t="inlineStr">
         <is>
-          <t>3290400757</t>
-        </is>
-      </c>
-      <c r="K435" s="6" t="inlineStr"/>
+          <t>3290400724</t>
+        </is>
+      </c>
+      <c r="K435" s="8" t="inlineStr">
+        <is>
+          <t>http://cs-izumo.jp/</t>
+        </is>
+      </c>
       <c r="L435" s="6" t="inlineStr"/>
     </row>
     <row r="436">
@@ -33223,7 +33193,7 @@
       </c>
       <c r="B436" s="7" t="inlineStr">
         <is>
-          <t>穂なみデイサービスセンターみなみ</t>
+          <t>やまねこデイサービス</t>
         </is>
       </c>
       <c r="C436" s="6" t="inlineStr">
@@ -33233,40 +33203,36 @@
       </c>
       <c r="D436" s="7" t="inlineStr">
         <is>
-          <t>里方町116番地</t>
+          <t>島根県出雲市芦渡町789-2</t>
         </is>
       </c>
       <c r="E436" s="6" t="inlineStr">
         <is>
-          <t>0853-20-1218</t>
+          <t>0853-31-6971</t>
         </is>
       </c>
       <c r="F436" s="6" t="inlineStr">
         <is>
-          <t>0853-20-1219</t>
+          <t>0853-31-6972</t>
         </is>
       </c>
       <c r="G436" s="6" t="inlineStr"/>
       <c r="H436" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="I436" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人コミュニティサポートいずも</t>
+          <t>株式会社ラッシュ</t>
         </is>
       </c>
       <c r="J436" s="6" t="inlineStr">
         <is>
-          <t>3290400724</t>
-        </is>
-      </c>
-      <c r="K436" s="8" t="inlineStr">
-        <is>
-          <t>http://cs-izumo.jp/</t>
-        </is>
-      </c>
+          <t>3290400807</t>
+        </is>
+      </c>
+      <c r="K436" s="6" t="inlineStr"/>
       <c r="L436" s="6" t="inlineStr"/>
     </row>
     <row r="437">
@@ -33277,7 +33243,7 @@
       </c>
       <c r="B437" s="7" t="inlineStr">
         <is>
-          <t>やまねこデイサービス</t>
+          <t>連珠　出雲四絡</t>
         </is>
       </c>
       <c r="C437" s="6" t="inlineStr">
@@ -33287,90 +33253,40 @@
       </c>
       <c r="D437" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市芦渡町789-2</t>
+          <t>島根県出雲市小山町633-1</t>
         </is>
       </c>
       <c r="E437" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6971</t>
+          <t>0853-25-7557</t>
         </is>
       </c>
       <c r="F437" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6972</t>
+          <t>0853-25-7557</t>
         </is>
       </c>
       <c r="G437" s="6" t="inlineStr"/>
       <c r="H437" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="I437" s="7" t="inlineStr">
         <is>
-          <t>株式会社ラッシュ</t>
+          <t>株式会社マリーナ</t>
         </is>
       </c>
       <c r="J437" s="6" t="inlineStr">
         <is>
-          <t>3290400807</t>
+          <t>3290400732</t>
         </is>
       </c>
       <c r="K437" s="6" t="inlineStr"/>
       <c r="L437" s="6" t="inlineStr"/>
     </row>
-    <row r="438">
-      <c r="A438" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型通所介護</t>
-        </is>
-      </c>
-      <c r="B438" s="7" t="inlineStr">
-        <is>
-          <t>連珠　出雲四絡</t>
-        </is>
-      </c>
-      <c r="C438" s="6" t="inlineStr">
-        <is>
-          <t>出雲</t>
-        </is>
-      </c>
-      <c r="D438" s="7" t="inlineStr">
-        <is>
-          <t>島根県出雲市小山町633-1</t>
-        </is>
-      </c>
-      <c r="E438" s="6" t="inlineStr">
-        <is>
-          <t>0853-25-7557</t>
-        </is>
-      </c>
-      <c r="F438" s="6" t="inlineStr">
-        <is>
-          <t>0853-25-7557</t>
-        </is>
-      </c>
-      <c r="G438" s="6" t="inlineStr"/>
-      <c r="H438" s="7" t="inlineStr">
-        <is>
-          <t>平日,土曜日</t>
-        </is>
-      </c>
-      <c r="I438" s="7" t="inlineStr">
-        <is>
-          <t>株式会社マリーナ</t>
-        </is>
-      </c>
-      <c r="J438" s="6" t="inlineStr">
-        <is>
-          <t>3290400732</t>
-        </is>
-      </c>
-      <c r="K438" s="6" t="inlineStr"/>
-      <c r="L438" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L438"/>
+  <autoFilter ref="A1:L437"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
@@ -33404,266 +33320,260 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K190" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K198" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K217" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K218" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K224" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K230" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K235" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K239" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K242" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K243" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K255" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K259" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K261" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K262" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K263" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K271" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K279" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K282" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K288" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K292" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K293" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K296" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K304" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K305" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K310" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K311" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K313" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K314" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K316" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K320" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K321" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K322" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K325" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K326" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K327" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K328" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K331" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K332" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K336" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K337" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K338" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K339" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K343" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K345" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K346" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K347" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K348" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K349" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K350" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K351" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K352" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K353" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K354" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K356" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K357" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K358" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K359" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K360" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K361" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K362" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K363" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K364" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K365" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K366" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K367" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K370" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K371" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K372" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K373" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K374" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K379" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L389" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L390" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K404" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K407" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K411" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K414" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K417" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K419" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K420" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K421" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K422" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K427" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L427" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K428" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L428" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K429" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K430" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K431" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K432" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K434" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K436" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K190" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K198" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K217" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K224" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K235" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K239" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K242" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K243" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K255" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K259" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K261" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K262" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K263" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K271" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K279" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K282" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K288" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K292" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K293" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K296" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K304" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K305" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K310" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K311" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K313" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K314" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K316" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K320" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K321" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K322" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K325" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K326" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K327" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K328" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K331" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K332" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K336" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K337" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K338" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K339" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K343" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K345" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K346" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K347" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K348" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K349" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K350" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K351" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K352" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K353" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K354" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K356" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K357" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K358" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K359" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K360" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K361" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K362" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K363" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K364" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K365" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K366" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K367" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K370" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K371" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K372" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K373" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K374" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K379" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L389" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L390" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K399" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K407" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K416" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K418" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K419" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K420" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K421" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K426" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L426" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K427" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L427" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K428" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K429" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K430" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K431" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K433" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K435" r:id="rId286"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34028,7 +33938,7 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>http://www.w-himawari.jp/nursing</t>
+          <t>https://www.w-himawari.jp/kaigo/</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr"/>
@@ -34167,7 +34077,7 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>http://www.w-himawari.jp/nursing</t>
+          <t>https://www.w-himawari.jp/kaigo/</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr"/>
@@ -34459,7 +34369,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>http://www.ssw.or.jp/facilities/seniors/tenjin/1476</t>
+          <t>https://www.ssw.or.jp/</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr"/>
@@ -34800,11 +34710,7 @@
           <t>3290400120</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>http://www.asunarohoikuen.ed.jp/top/index.html</t>
-        </is>
-      </c>
+      <c r="J3" s="6" t="inlineStr"/>
       <c r="K3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
@@ -35027,11 +34933,7 @@
           <t>3290400815</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>http://yama-boushi.com/</t>
-        </is>
-      </c>
+      <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
@@ -35451,18 +35353,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35798,7 +35698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -35817,7 +35717,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>地域密着型通所介護（出雲市・45件）</t>
+          <t>地域密着型通所介護（出雲市・44件）</t>
         </is>
       </c>
     </row>
@@ -35977,30 +35877,32 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>あんのん大社</t>
+          <t>あんのんの里川跡</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>大社</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市大社町杵築西1735</t>
+          <t>荻杼町666-1</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4780</t>
+          <t>0853-31-4600</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4781</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
+          <t>0853-31-4601</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>平日,祝日</t>
@@ -36013,7 +35915,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>3290400799</t>
+          <t>3270402138</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
@@ -36022,7 +35924,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>あんのんの里川跡</t>
+          <t>出雲市里家センター</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -36032,21 +35934,21 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>荻杼町666-1</t>
+          <t>出雲市乙立町3162番地</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4600</t>
+          <t>0853-45-0378</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>0853-31-4601</t>
+          <t>0853-45-0370</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -36055,12 +35957,12 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>株式会社ハート</t>
+          <t>株式会社蔵西</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>3270402138</t>
+          <t>3270401551</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr"/>
@@ -36069,7 +35971,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>出雲市里家センター</t>
+          <t>ウェルファ出雲デイサービスセンターかえで</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -36079,35 +35981,33 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>出雲市乙立町3162番地</t>
+          <t>島根県出雲市塩冶神前１－６－２７CASA神前１階CASA神前１階</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>0853-45-0378</t>
+          <t>０８５３－２５－７１１０</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>0853-45-0370</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>12</v>
-      </c>
+          <t>０８５３－２５－７００８</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>株式会社蔵西</t>
+          <t>ボンウエルファ株式会社</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>3270401551</t>
+          <t>3270402666</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -36116,7 +36016,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>ウェルファ出雲デイサービスセンターかえで</t>
+          <t>えきまえデイサービス　夢のむら</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -36126,83 +36026,89 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市塩冶神前１－６－２７CASA神前１階CASA神前１階</t>
+          <t>出雲市塩冶町　980-3</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２５－７１１０</t>
+          <t>0853-21-0986</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２５－７００８</t>
+          <t>0853-23-0197</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>ボンウエルファ株式会社</t>
+          <t>有限会社ケアサービス出雲</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>3270402666</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
+          <t>3270401171</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>https://care-service-izumo.biz/</t>
+        </is>
+      </c>
       <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>えきまえデイサービス　夢のむら</t>
+          <t>NPO法人たすけあい平田デイサービスセンターさわやか</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>出雲市塩冶町　980-3</t>
+          <t>島根県出雲市西代町1032-4</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>0853-21-0986</t>
+          <t>0853-31-6500</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>0853-23-0197</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
+          <t>0853-31-6501</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>有限会社ケアサービス出雲</t>
+          <t>特定非営利活動法人たすけあい平田デイサービスセンターさわやか</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>3270401171</t>
+          <t>3270402781</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>https://care-service-izumo.biz/</t>
+          <t>http://www.npo.lsnet.ne.jp/tasukeaihirata/</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr"/>
@@ -36210,50 +36116,48 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NPO法人たすけあい平田デイサービスセンターさわやか</t>
+          <t>介護予防センター　早稲田イーライフ出雲</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市西代町1032-4</t>
+          <t>大津新崎町1丁目29番地1</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6500</t>
+          <t>0853－25－8412</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6501</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>5</v>
-      </c>
+          <t>0853－25－8413</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人たすけあい平田デイサービスセンターさわやか</t>
+          <t>株式会社　中林建築設計事務所</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>3270402781</t>
+          <t>3270402310</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>http://www.npo.lsnet.ne.jp/tasukeaihirata/</t>
+          <t>http://www.h-sweet-home.com</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr"/>
@@ -36261,30 +36165,32 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>介護予防センター　早稲田イーライフ出雲</t>
+          <t>介護予防センター　早稲田イーライフきらり</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>湖陵</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>大津新崎町1丁目29番地1</t>
+          <t>島根県出雲市湖陵町二部1192番地1</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8412</t>
+          <t>0853-43-8080</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8413</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
+          <t>0853-43-7006</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>平日,祝日</t>
@@ -36292,17 +36198,17 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>株式会社　中林建築設計事務所</t>
+          <t>株式会社中林建築設計事務所</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>3270402310</t>
+          <t>3270401916</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>http://www.h-sweet-home.com</t>
+          <t>http://www.h-sweet-home.com/</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr"/>
@@ -36310,50 +36216,48 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>介護予防センター　早稲田イーライフきらり</t>
+          <t>ケアサポート　相生</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>湖陵</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市湖陵町二部1192番地1</t>
+          <t>出雲市今市町７４１－５</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0853-43-8080</t>
+          <t>0853-24-7733</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>0853-43-7006</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>100</v>
-      </c>
+          <t>0853-24-7738</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>株式会社中林建築設計事務所</t>
+          <t>社会福祉法人壽光会</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>3270401916</t>
+          <t>3270401114</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>http://www.h-sweet-home.com/</t>
+          <t>https://jukokai.jp/</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr"/>
@@ -36361,101 +36265,103 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>ケアサポート　相生</t>
+          <t>ココ・リハ平田</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>出雲市今市町７４１－５</t>
+          <t>島根県出雲市西平田町104番地3</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>0853-24-7733</t>
+          <t>0853－25－8400</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>0853-24-7738</t>
+          <t>0853－25－8401</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人壽光会</t>
+          <t>株式会社　建装</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>3270401114</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>https://jukokai.jp/</t>
-        </is>
-      </c>
+          <t>3270402336</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>ココ・リハ平田</t>
+          <t>茶話本舗デイサービス出雲</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市西平田町104番地3</t>
+          <t>島根県出雲市大津新崎町5-38-1</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8400</t>
+          <t>0853-25-8535</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>0853－25－8401</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr"/>
+          <t>0853-25-8536</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,日曜日,祝日</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>株式会社　建装</t>
+          <t>株式会社ドリームシアター</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>3270402336</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
+          <t>3270402534</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>https://sawaizumo.wixsite.com/home</t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>茶話本舗デイサービス出雲</t>
+          <t>社会福祉法人静和会プライム清流園デイサービスセンター</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -36465,22 +36371,20 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市大津新崎町5-38-1</t>
+          <t>島根県出雲市大津町3529</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8535</t>
+          <t>0583-25-8356</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8536</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10</v>
-      </c>
+          <t>0853-25-8376</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,日曜日,祝日</t>
@@ -36488,17 +36392,17 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>株式会社ドリームシアター</t>
+          <t>社会福祉法人静和会</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>3270402534</t>
+          <t>3290400773</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>https://sawaizumo.wixsite.com/home</t>
+          <t>https://www.seiryuuen.com/</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr"/>
@@ -36506,48 +36410,48 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人静和会プライム清流園デイサービスセンター</t>
+          <t>社会福祉法人やまゆり　通所やまゆり</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>佐田</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市大津町3529</t>
+          <t>島根県出雲市佐田町一窪田1961番地５</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>0583-25-8356</t>
+          <t>0853-85-8100</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8376</t>
+          <t>0853-85-2929</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,日曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人静和会</t>
+          <t>社会福祉法人やまゆり</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>3290400773</t>
+          <t>3270401361</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>http://www.seiryuuen.com/page533016.html</t>
+          <t>http://www.izumo-yamayuri.or.jp</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr"/>
@@ -36555,48 +36459,48 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり　通所やまゆり</t>
+          <t>出東デイサービスセンター</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>佐田</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市佐田町一窪田1961番地５</t>
+          <t>島根県出雲市斐川町三分市1077</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>0853-85-8100</t>
+          <t>0853-63-3777</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>0853-85-2929</t>
+          <t>0853-63-7007</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり</t>
+          <t>社会福祉法人出東福祉会</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>3270401361</t>
+          <t>3271600144</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>http://www.izumo-yamayuri.or.jp</t>
+          <t>https://syuttou-fukushikai.net/day/</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr"/>
@@ -36604,27 +36508,27 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>出東デイサービスセンター</t>
+          <t>笑庵ことぶき通所介護事業所</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町三分市1077</t>
+          <t>古志町344</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>0853-63-3777</t>
+          <t>0853-25-7701</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>0853-63-7007</t>
+          <t>0853-25-7702</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -36635,17 +36539,17 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人出東福祉会</t>
+          <t>社会福祉法人ことぶき福祉会</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>3271600144</t>
+          <t>3270401882</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>https://syuttou-fukushikai.net/day/</t>
+          <t>https://kotobuki1071.jimdofree.com/</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr"/>
@@ -36653,48 +36557,48 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>笑庵ことぶき通所介護事業所</t>
+          <t>通所　かがやきの家</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>佐田</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>古志町344</t>
+          <t>島根県出雲市佐田町須佐736番地2</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7701</t>
+          <t>0853-84-9300</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7702</t>
+          <t>0853-84-9300</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人ことぶき福祉会</t>
+          <t>社会福祉法人やまゆり</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>3270401882</t>
+          <t>3270401403</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>https://kotobuki1071.jimdofree.com/</t>
+          <t>http://www.izumo-yamayuri.or.jp</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr"/>
@@ -36702,56 +36606,54 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>通所　かがやきの家</t>
+          <t>通所介護長浜味覚亭</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>佐田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市佐田町須佐736番地2</t>
+          <t>出雲市西園町500番地1</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>0853-84-9300</t>
+          <t>0853-28-2828</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>0853-84-9300</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr"/>
+          <t>0853-28-2028</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり</t>
+          <t>株式会社蔵西</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>3270401403</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>http://www.izumo-yamayuri.or.jp</t>
-        </is>
-      </c>
+          <t>3270401288</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>通所介護長浜味覚亭</t>
+          <t>デイサービス　こひまり</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -36761,22 +36663,20 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>出雲市西園町500番地1</t>
+          <t>島根県出雲市馬木町224-1</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>0853-28-2828</t>
+          <t>０８５３－４８－９０５７</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>0853-28-2028</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>18</v>
-      </c>
+          <t>０８５３－４８－００４７</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -36784,12 +36684,12 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>株式会社蔵西</t>
+          <t>株式会社ひまり</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>3270401288</t>
+          <t>3290400567</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr"/>
@@ -36798,7 +36698,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　こひまり</t>
+          <t>デイサービス　グッドライフ</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -36808,20 +36708,22 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市馬木町224-1</t>
+          <t>島根県出雲市塩冶善行町14-3</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>０８５３－４８－９０５７</t>
+          <t>0853-27-9991</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>０８５３－４８－００４７</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr"/>
+          <t>0853-27-9992</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>15</v>
+      </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -36829,21 +36731,25 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>株式会社ひまり</t>
+          <t>株式会社　コスモス</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>3290400567</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr"/>
+          <t>3270402120</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cosmos-izumo.jp</t>
+        </is>
+      </c>
       <c r="K22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　グッドライフ</t>
+          <t>デイサービス　さくら</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -36853,22 +36759,20 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市塩冶善行町14-3</t>
+          <t>矢尾町273番地プライム有限会社プライム有限会社</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9991</t>
+          <t>0853-25-0027</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9992</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>15</v>
-      </c>
+          <t>0853-25-0020</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -36876,25 +36780,21 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>株式会社　コスモス</t>
+          <t>プライム有限会社</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>3270402120</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>https://www.cosmos-izumo.jp</t>
-        </is>
-      </c>
+          <t>3270402641</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　さくら</t>
+          <t>デイサービス　なすの花</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -36904,17 +36804,17 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>矢尾町273番地プライム有限会社プライム有限会社</t>
+          <t>島根県出雲市白枝町７８１－８</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0027</t>
+          <t>０８５３－２０－１２８８</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0020</t>
+          <t>０８５３－２０－１２８７</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
@@ -36925,12 +36825,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>プライム有限会社</t>
+          <t>株式会社スマイル・ガーデン</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>3270402641</t>
+          <t>3270401635</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr"/>
@@ -36939,7 +36839,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　なすの花</t>
+          <t>デイサービス　春の野</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -36949,42 +36849,48 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市白枝町７８１－８</t>
+          <t>島根県出雲市小山町３３４番地板倉ビル１０３号室板倉ビル１０３号室</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２０－１２８８</t>
+          <t>0853-25-8550</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>０８５３－２０－１２８７</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr"/>
+          <t>0853-25-8550</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>株式会社スマイル・ガーデン</t>
+          <t>株式会社ＨＯＬＹ</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3270401635</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr"/>
+          <t>3290400781</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/デイサービス春の野/100094930075195/</t>
+        </is>
+      </c>
       <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　春の野</t>
+          <t>ﾃﾞｲｻｰﾋﾞｽ　ひまり</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -36994,48 +36900,42 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市小山町３３４番地板倉ビル１０３号室板倉ビル１０３号室</t>
+          <t>出雲市馬木町７５８番地２</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8550</t>
+          <t>0853-48-9135</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>0853-25-8550</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>20</v>
-      </c>
+          <t>0853-48-2670</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>株式会社ＨＯＬＹ</t>
+          <t>株式会社ひまり</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>3290400781</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/people/デイサービス春の野/100094930075195/</t>
-        </is>
-      </c>
+          <t>3270402047</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>ﾃﾞｲｻｰﾋﾞｽ　ひまり</t>
+          <t>デイサービス　ゆうらいふ</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -37045,85 +36945,91 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>出雲市馬木町７５８番地２</t>
+          <t>島根県出雲市荒茅町3501</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>0853-48-9135</t>
+          <t>0853-28-0385</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>0853-48-2670</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr"/>
+          <t>0853-28-0339</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>株式会社ひまり</t>
+          <t>株式会社ライフサポート</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>3270402047</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr"/>
+          <t>3270401437</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>http://youlife-n.com</t>
+        </is>
+      </c>
       <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>デイサービス　ゆうらいふ</t>
+          <t>デイサービス金太郎の家やまぶき</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市荒茅町3501</t>
+          <t>島根県出雲市斐川町学頭1511番地1金太郎の家金太郎の家</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>0853-28-0385</t>
+          <t>0853-72-5110</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>0853-28-0339</t>
+          <t>0853-72-5192</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>株式会社ライフサポート</t>
+          <t>社会福祉法人金太郎の家</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>3270401437</t>
+          <t>3270402419</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>http://youlife-n.com</t>
+          <t>https://www.kintarounoie.jp/</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr"/>
@@ -37131,7 +37037,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>デイサービス金太郎の家やまぶき</t>
+          <t>デイサービス新川</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -37141,17 +37047,17 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町学頭1511番地1金太郎の家金太郎の家</t>
+          <t>島根県出雲市斐川町大字上庄原字上新川1634番地5</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>0853-72-5110</t>
+          <t>0853-73-7363</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>0853-72-5192</t>
+          <t>0853-73-7363</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -37159,22 +37065,22 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人金太郎の家</t>
+          <t>株式会社ハピネライフ一光</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>3270402419</t>
+          <t>3271600664</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>https://www.kintarounoie.jp/</t>
+          <t>http://www.h-ikkou.co.jp</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr"/>
@@ -37182,50 +37088,50 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>デイサービス新川</t>
+          <t>デイサービス寿生の家</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町大字上庄原字上新川1634番地5</t>
+          <t>出雲市上塩冶町2854-5</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>0853-73-7363</t>
+          <t>0853-25-0241</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>0853-73-7363</t>
+          <t>0853-25-0285</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>株式会社ハピネライフ一光</t>
+          <t>壽生会</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>3271600664</t>
+          <t>3270401411</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>http://www.h-ikkou.co.jp</t>
+          <t>http://juseikai.jp/</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr"/>
@@ -37233,7 +37139,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>デイサービス寿生の家</t>
+          <t>デイサービスセンター翔雲</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -37243,48 +37149,42 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>出雲市上塩冶町2854-5</t>
+          <t>島根県出雲市今市町822-22</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0241</t>
+          <t>0853-21‐5582</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>0853-25-0285</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>15</v>
-      </c>
+          <t>0853-23-5584</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>壽生会</t>
+          <t>株式会社高砂屋</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>3270401411</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>http://juseikai.jp/</t>
-        </is>
-      </c>
+          <t>3290400765</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>デイサービスセンター翔雲</t>
+          <t>デイサービスセンター高砂</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -37294,12 +37194,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市今市町822-22</t>
+          <t>島根県出雲市今市町822番地22</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>0853-21‐5582</t>
+          <t>0853-21-5582</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -37320,7 +37220,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>3290400765</t>
+          <t>3290400716</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr"/>
@@ -37329,43 +37229,43 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>デイサービスセンター高砂</t>
+          <t>デイサービス向日葵の家</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市今市町822番地22</t>
+          <t>出雲市斐川町荘原3169-28</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>0853-21-5582</t>
+          <t>0853-72-5109</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>0853-23-5584</t>
+          <t>0853-27-9737</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>株式会社高砂屋</t>
+          <t>有限会社　司</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>3290400716</t>
+          <t>3271600565</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr"/>
@@ -37374,7 +37274,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>デイサービス向日葵の家</t>
+          <t>デイサービスMILK新</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -37384,20 +37284,22 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>出雲市斐川町荘原3169-28</t>
+          <t>島根県出雲市斐川町上庄原1649番地</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>0853-72-5109</t>
+          <t>0853-31-9722</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9737</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr"/>
+          <t>0853-31-9733</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>25</v>
+      </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -37405,12 +37307,12 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>有限会社　司</t>
+          <t>株式会社　Care　Innovation</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>3271600565</t>
+          <t>3290400526</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr"/>
@@ -37419,31 +37321,31 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>デイサービスMILK新</t>
+          <t>デイサービスもくれん</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町上庄原1649番地</t>
+          <t>出雲市松寄下町1286－1</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>0853-31-9722</t>
+          <t>0853-25-7230</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>0853-31-9733</t>
+          <t>0853-25-7231</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
@@ -37452,21 +37354,29 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>株式会社　Care　Innovation</t>
+          <t>株式会社もくれん</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>3290400526</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr"/>
-      <c r="K35" s="6" t="inlineStr"/>
+          <t>3270401528</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>https://www.izumo-mokuren.com/</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>https://www.izumo-mokuren.com/price/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>デイサービスもくれん</t>
+          <t>デイサービスもくれん・荒茅</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -37476,21 +37386,21 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>出雲市松寄下町1286－1</t>
+          <t>出雲市荒茅町2780番地32</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7230</t>
+          <t>0853-27-9651</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7231</t>
+          <t>0853-27-9652</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -37504,7 +37414,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>3270401528</t>
+          <t>3270401965</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -37521,7 +37431,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>デイサービスもくれん・荒茅</t>
+          <t>デイサービスゆうゆう広場</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -37531,21 +37441,21 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>出雲市荒茅町2780番地32</t>
+          <t>知井宮町５－１</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9651</t>
+          <t>0853-23-8762</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>0853-27-9652</t>
+          <t>0853-22-8491</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
@@ -37554,29 +37464,25 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>株式会社もくれん</t>
+          <t>エイコー電子工業株式会社</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>3270401965</t>
+          <t>3270401650</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>https://www.izumo-mokuren.com/</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>https://www.izumo-mokuren.com/price/</t>
-        </is>
-      </c>
+          <t>https://eikoh-elc.com</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>デイサービスゆうゆう広場</t>
+          <t>ハピネデイサービスセンター出雲</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -37586,21 +37492,21 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>知井宮町５－１</t>
+          <t>出雲市渡橋町303番地3</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>0853-23-8762</t>
+          <t>0853-23-8840</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>0853-22-8491</t>
+          <t>0853-23-2269</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -37609,17 +37515,17 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>エイコー電子工業株式会社</t>
+          <t>株式会社ハピネライフ一光</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>3270401650</t>
+          <t>3270400538</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>https://eikoh-elc.com</t>
+          <t>https://www.hapine.com/</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr"/>
@@ -37627,7 +37533,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>ハピネデイサービスセンター出雲</t>
+          <t>稗原デイサービスセンター　やまゆり</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -37637,40 +37543,38 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>出雲市渡橋町303番地3</t>
+          <t>島根県出雲市稗原町1724番地</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>0853-23-8840</t>
+          <t>0853-77-2497</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>0853-23-2269</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>15</v>
-      </c>
+          <t>0853-77-2497</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr"/>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>株式会社ハピネライフ一光</t>
+          <t>社会福祉法人やまゆり</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>3270400538</t>
+          <t>3290400708</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>https://www.hapine.com/</t>
+          <t>http://www.izumo-yamayuri.or.jp</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr"/>
@@ -37678,48 +37582,48 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>稗原デイサービスセンター　やまゆり</t>
+          <t>ひかわ生協デイサービス　ふらみんご</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市稗原町1724番地</t>
+          <t>島根県出雲市斐川町直江４８８３番地１</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>0853-77-2497</t>
+          <t>0853-72-0353</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>0853-77-2497</t>
+          <t>0853-72-0322</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>社会福祉法人やまゆり</t>
+          <t>ひかわ医療生活協同組合</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>3290400708</t>
+          <t>3271600656</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>http://www.izumo-yamayuri.or.jp</t>
+          <t>https://www.hikawa-hp.com</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr"/>
@@ -37727,126 +37631,126 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>ひかわ生協デイサービス　ふらみんご</t>
+          <t>フロディいずも</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町直江４８８３番地１</t>
+          <t>塩冶有原町５丁目３６番地</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>0853-72-0353</t>
+          <t>0853-25-7711</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>0853-72-0322</t>
+          <t>0853-25-7791</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>ひかわ医療生活協同組合</t>
+          <t>フロディ出雲</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>3271600656</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hikawa-hp.com</t>
-        </is>
-      </c>
+          <t>3290400583</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr"/>
       <c r="K41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>フロディいずも</t>
+          <t>穂なみデイサービスセンターひかわ</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>出雲</t>
+          <t>斐川</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>塩冶有原町５丁目３６番地</t>
+          <t>島根県出雲市斐川町上直江２４３－３</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7711</t>
+          <t>0853-25-7946</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7791</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
+          <t>0853-25-7948</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>平日</t>
+          <t>平日,土曜日,祝日</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>フロディ出雲</t>
+          <t>特定非営利活動法人コミュニティサポートいずも</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>3290400583</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr"/>
+          <t>3290400674</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>http://cs-izumo.jp/</t>
+        </is>
+      </c>
       <c r="K42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>穂なみデイサービスセンターひかわ</t>
+          <t>穂なみデイサービスセンターひらた</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>斐川</t>
+          <t>平田</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市斐川町上直江２４３－３</t>
+          <t>島根県出雲市平田町1953－3</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7946</t>
+          <t>0853－62－9365</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>0853-25-7948</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>18</v>
-      </c>
+          <t>0853－62－9366</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>平日,土曜日,祝日</t>
@@ -37859,40 +37763,36 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>3290400674</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>http://cs-izumo.jp/</t>
-        </is>
-      </c>
+          <t>3290400757</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr"/>
       <c r="K43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>穂なみデイサービスセンターひらた</t>
+          <t>穂なみデイサービスセンターみなみ</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>平田</t>
+          <t>出雲</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市平田町1953－3</t>
+          <t>里方町116番地</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>0853－62－9365</t>
+          <t>0853-20-1218</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>0853－62－9366</t>
+          <t>0853-20-1219</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -37908,16 +37808,20 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>3290400757</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr"/>
+          <t>3290400724</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>http://cs-izumo.jp/</t>
+        </is>
+      </c>
       <c r="K44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>穂なみデイサービスセンターみなみ</t>
+          <t>やまねこデイサービス</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -37927,46 +37831,42 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>里方町116番地</t>
+          <t>島根県出雲市芦渡町789-2</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>0853-20-1218</t>
+          <t>0853-31-6971</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>0853-20-1219</t>
+          <t>0853-31-6972</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>平日,土曜日,祝日</t>
+          <t>平日,祝日</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>特定非営利活動法人コミュニティサポートいずも</t>
+          <t>株式会社ラッシュ</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>3290400724</t>
-        </is>
-      </c>
-      <c r="J45" s="8" t="inlineStr">
-        <is>
-          <t>http://cs-izumo.jp/</t>
-        </is>
-      </c>
+          <t>3290400807</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>やまねこデイサービス</t>
+          <t>連珠　出雲四絡</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -37976,113 +37876,68 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>島根県出雲市芦渡町789-2</t>
+          <t>島根県出雲市小山町633-1</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6971</t>
+          <t>0853-25-7557</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>0853-31-6972</t>
+          <t>0853-25-7557</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>平日,祝日</t>
+          <t>平日,土曜日</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>株式会社ラッシュ</t>
+          <t>株式会社マリーナ</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>3290400807</t>
+          <t>3290400732</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr"/>
       <c r="K46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>連珠　出雲四絡</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>出雲</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>島根県出雲市小山町633-1</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>0853-25-7557</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>0853-25-7557</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr"/>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>平日,土曜日</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>株式会社マリーナ</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>3290400732</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr"/>
-      <c r="K47" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40462,7 +40317,7 @@
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>http://www.jaizumo.or.jp/welfare</t>
+          <t>https://jaizumo-fukushikai.jp/</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr"/>
@@ -41195,7 +41050,7 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>http://www.izumo-tokushukai.jp/homevisit</t>
+          <t>https://www.izumo-tokushukai.jp/homevisit/</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr"/>
@@ -41434,11 +41289,7 @@
           <t>3260490267</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>https://izumo.mypl.net/shop/00000369278/</t>
-        </is>
-      </c>
+      <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
@@ -42612,14 +42463,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42900,7 +42750,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>http://www/kandokai.jp/</t>
+          <t>http://www.kandokai.jp/clinic/</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr"/>
@@ -44368,11 +44218,7 @@
           <t>3271600532</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>http://purelife-shimane.com/dayserv/index</t>
-        </is>
-      </c>
+      <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
@@ -45387,7 +45233,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>http://www.jaizumo.or.jp/welfare</t>
+          <t>https://jaizumo-fukushikai.jp/</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr"/>
@@ -45455,22 +45301,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46622,7 +46467,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>http://www.harasho.co.jp/inquiry/list.html#smile_izumo</t>
+          <t>https://www.harasho.co.jp/company/office/smile-care-office/smile-izumo</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr"/>
@@ -47047,7 +46892,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>http://genkido-info.jimdo.com/</t>
+          <t>https://genkido-info.jimdofree.com/</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr"/>

--- a/jigyosho/izumo_kaigo_list.xlsx
+++ b/jigyosho/izumo_kaigo_list.xlsx
@@ -14012,7 +14012,11 @@
           <t>3260490267</t>
         </is>
       </c>
-      <c r="K66" s="6" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lifecreate-grow.com/grow</t>
+        </is>
+      </c>
       <c r="L66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
@@ -33320,260 +33324,261 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K190" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K198" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K217" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K224" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K235" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K239" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K242" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K243" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K255" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K259" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K261" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K262" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K263" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K271" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K279" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K282" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K288" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K292" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K293" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K296" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K304" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K305" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K310" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K311" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K313" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K314" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K316" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K320" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K321" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K322" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K325" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K326" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K327" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K328" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K331" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K332" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K336" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K337" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K338" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K339" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K343" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K345" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K346" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K347" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K348" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K349" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K350" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K351" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K352" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K353" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K354" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K356" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K357" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K358" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K359" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K360" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K361" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K362" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K363" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K364" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K365" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K366" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K367" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K370" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K371" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K372" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K373" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K374" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K379" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L389" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L390" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K399" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K407" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K416" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K418" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K419" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K420" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K421" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K426" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L426" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K427" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L427" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K428" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K429" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K430" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K431" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K433" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K435" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K190" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K198" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K217" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K224" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K235" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K239" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K242" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K243" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K255" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K259" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K261" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K262" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K263" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K271" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K279" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K282" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K288" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K292" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K293" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K296" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K304" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K305" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K310" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K311" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K313" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K314" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K316" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K320" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K321" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K322" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K325" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K326" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K327" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K328" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K331" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K332" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K336" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K337" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K338" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K339" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K343" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K345" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K346" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K347" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K348" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K349" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K350" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K351" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K352" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K353" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K354" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L355" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K356" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K357" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K358" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L358" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K359" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K360" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K361" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K362" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K363" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K364" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K365" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K366" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K367" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K370" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K371" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K372" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K373" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K374" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K379" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L389" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L390" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K399" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K407" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K416" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K418" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K419" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K420" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K421" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K426" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L426" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K427" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L427" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K428" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K429" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K430" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K431" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K433" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K435" r:id="rId287"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41289,7 +41294,11 @@
           <t>3260490267</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lifecreate-grow.com/grow</t>
+        </is>
+      </c>
       <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
@@ -42463,13 +42472,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
